--- a/outputs/huawei-permission-application/申请数据权限及使用说明-徒步手表项目填写版.xlsx
+++ b/outputs/huawei-permission-application/申请数据权限及使用说明-徒步手表项目填写版.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业开发者" sheetId="1" r:id="R692c7f581a9743f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人开发者" sheetId="2" r:id="Rc2f1ba1e8076401c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业文字介绍（必填）" sheetId="3" r:id="R4a30c716255640d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业项目负责人联系方式（必填）" sheetId="4" r:id="R45bd76fc0055460f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营业执照（选填）" sheetId="5" r:id="Rf43e860318dd4493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用信息（必填）" sheetId="6" r:id="R30cc42e4682742dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充说明（必填）" sheetId="7" r:id="Rd336d563d490427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业开发者" sheetId="1" r:id="R8904ff6be43547d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人开发者" sheetId="2" r:id="Rf02210167ca94ff7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业文字介绍（必填）" sheetId="3" r:id="Rf02f5b2f890e4e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业项目负责人联系方式（必填）" sheetId="4" r:id="Rcb109e37446b45c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营业执照（选填）" sheetId="5" r:id="Rb02a753f4a9c4583"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用信息（必填）" sheetId="6" r:id="Rbfc7cf9f9d3846ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充说明（必填）" sheetId="7" r:id="R71c38ea27c484834"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -505,8 +505,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>使用场景：本项目当前首发范围为 Apple Watch / watchOS 徒步导航 MVP，华为生态仅作为 Apple Watch MVP 之后的平台验证预研。手机侧验证 App 在用户主动打开并选择徒步路线后，需要发现并确认已配对的 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，读取设备随机标识符、名称、电量、连接状态、应用安装状态等基础信息，用于判断是否可以向目标手表下发路线数据；当设备在线但未安装验证端应用时，在手机侧提示用户先安装或打开对应手表端验证应用；当设备在线且验证端应用可用时，才允许用户手动发起路线同步。
-需求：计划先验证 HarmonyOS / 华为手机线，随后验证非华为 Android 手机线；不把 iPhone + 华为手表作为深度联动主路径。需要在 WATCH 5 / WATCH 4 上验证完整手表 App，在 WATCH GT 6 / GT 5 上验证轻量应用或手机协同路径。手机侧与手表侧通信只在用户主动进入路线同步/徒步验证流程时使用，申请材料中的能力均为待华为真机与 AGC 后台验证，不代表已上线或已实测结论。</x:v>
+        <x:v>使用场景：本次申请仅针对华为穿戴生态的户外徒步手表应用验证与后续上线准备。手机侧应用在用户主动打开并选择徒步路线后，需要发现并确认已配对的 HUAWEI WATCH 数字系列或 HUAWEI WATCH GT 系列设备，读取设备随机标识符、名称、电量、连接状态、应用安装状态等基础信息，用于判断是否可以向目标手表下发路线数据；当设备在线但未安装手表端应用或轻量协同能力不可用时，在手机侧提示用户先安装或打开对应手表端应用；当设备在线且手表端能力可用时，才允许用户手动发起路线同步。
+需求：计划先验证 HarmonyOS / 华为手机线，随后验证 Android 手机线。需要在 HUAWEI WATCH 5 / WATCH 4 上验证完整手表 App 路径，在 HUAWEI WATCH GT 6 / GT 5 上验证轻量应用或手机协同路径。手机侧与手表侧通信只在用户主动进入路线同步/徒步验证流程时使用，申请材料中的目标机型和能力仍以华为真机、SDK 文档和 AppGallery Connect 后台审核结果为准。</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
         <x:v>待补充截图：手机侧路线详情页 -&gt; 同步到华为手表 -&gt; 设备选择/连接状态页</x:v>
@@ -523,8 +523,8 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>使用场景：手机侧验证 App 在用户主动选择一条 GPX/路线 payload 并点击“同步到手表”后，向已配对的华为穿戴设备发送路线摘要、路线点位数据或导航指令，并接收手表端 ACK、安装结果、当前会话状态、偏航提醒状态、低电量状态等文本/JSON 消息。该能力用于验证徒步前路线下发、徒步中状态确认、结束后最小结果回传等闭环，不用于营销推送或无用户触发的通知。
-需求：手机侧形态包括 HarmonyOS / 华为手机验证 App 和 Android 手机验证 App；手表侧按 WATCH 数字系列完整应用与 GT 系列轻量/协同路径分别验证。发送内容主要为文本或 JSON；如后续验证 GPX 文件传输，仅限用户选定路线文件，不传输通讯录、相册、账号密码等无关个人数据。发送动作由用户在手机侧主动触发，优先要求手机 App 前台可见，手表端应用或轻量协同能力可用。目标机型优先 WATCH 5 / WATCH 4、WATCH GT 6 / GT 5，实际支持范围以真机和华为后台审核为准。</x:v>
+        <x:v>使用场景：手机侧应用在用户主动选择一条 GPX/路线 payload 并点击“同步到华为手表”后，向已配对的华为穿戴设备发送路线摘要、路线点位数据或导航指令，并接收手表端 ACK、安装结果、当前会话状态、偏航提醒状态、低电量状态等文本/JSON 消息。该能力用于华为手表徒步前路线下发、徒步中状态确认、偏航/低电量提醒状态同步、结束后最小结果回传等闭环，不用于营销推送或无用户触发的通知。
+需求：手机侧形态包括 HarmonyOS / 华为手机应用和 Android 手机应用；手表侧按 HUAWEI WATCH 数字系列完整应用与 WATCH GT 系列轻量/协同路径分别验证。发送内容主要为文本或 JSON；如后续验证 GPX 文件传输，仅限用户选定路线文件，不传输通讯录、相册、账号密码等无关个人数据。发送动作由用户在手机侧主动触发，优先要求手机 App 前台可见，手表端应用或轻量协同能力可用。目标机型优先 WATCH 5 / WATCH 4、WATCH GT 6 / GT 5，实际支持范围以真机和华为后台审核为准。</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
         <x:v>待补充截图：手机侧路线详情页 -&gt; 点击同步 -&gt; 手表端接收路线/ACK 状态页</x:v>
@@ -542,7 +542,7 @@
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>暂不申请。
-当前项目的 P0 华为验证重点是路线下发、ACK、连接/电量状态、手表端路线显示、偏航提醒和轨迹/状态回传。睡眠状态、佩戴状态等信息不作为本次权限申请的必需能力；若后续需要用于“是否佩戴手表后再开始徒步记录”等体验优化，将另行补充真实产品页面、用户授权路径和最小化使用说明。</x:v>
+当前华为申请重点是路线下发、ACK、连接/电量状态、手表端路线显示、偏航提醒和轨迹/状态回传。睡眠状态、佩戴状态等信息不作为本次权限申请的必需能力；若后续需要用于“确认用户佩戴手表后再开始徒步记录”等体验优化，将另行补充真实产品页面、用户授权路径和最小化使用说明。</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
         <x:v>不申请，暂无截图</x:v>
@@ -559,8 +559,8 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>使用场景：在徒步导航验证过程中，手机侧或手表侧需要读取已配对穿戴设备的加速度、陀螺仪等运动传感器信息，用于验证户外徒步中的运动状态判断、步频/运动趋势辅助分析、偏航提醒可信度辅助判断，以及运动后复盘中的运动片段标注。该数据只用于当前用户本次徒步会话的实时判断和复盘展示，不用于广告画像、与第三方共享或跨用户分析。
-需求：手机侧验证 App 计划覆盖 HarmonyOS / 华为手机和 Android 手机；手表侧优先 WATCH 5 / WATCH 4，GT 6 / GT 5 仅在目标机型和 SDK 支持时验证。当前仍处预研阶段，传感器采样频率、后台可用性、电量影响和机型差异均需要真机验证。若审核认为该能力与首轮路线同步验证无关，可先不申请此项，待 H3 户外能力验证阶段再单独申请。</x:v>
+        <x:v>使用场景：在华为手表徒步导航验证过程中，手机侧或手表侧需要读取已配对穿戴设备的加速度、陀螺仪等运动传感器信息，用于验证户外徒步中的运动状态判断、步频/运动趋势辅助分析、偏航提醒可信度辅助判断，以及运动后复盘中的运动片段标注。该数据只用于当前用户本次徒步会话的实时判断和复盘展示，不用于广告画像、与第三方共享或跨用户分析。
+需求：手机侧应用计划覆盖 HarmonyOS / 华为手机和 Android 手机；手表侧优先 WATCH 5 / WATCH 4，GT 6 / GT 5 仅在目标机型和 SDK 支持时验证。传感器采样频率、后台可用性、电量影响和机型差异均需要华为真机验证。若审核认为该能力与首轮路线同步验证无关，可先不申请此项，待户外能力验证阶段再单独申请。</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>待补充截图：徒步会话页/复盘页中的运动状态辅助展示；若首轮不申请则删除本行</x:v>
@@ -578,7 +578,7 @@
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>暂不申请。
-本项目不是医疗诊断或专业研究机构项目，首轮华为验证不需要控制或获取心率、心电图、PPG 等人体传感器原始数据。运动后复盘如需展示心率等健康数据，应优先通过用户明确授权的 Health Kit / Health Service Kit 标准健康数据接口读取汇总数据，并在后续单独提交健康数据权限申请、隐私政策和用户授权路径。</x:v>
+本项目不是医疗诊断或专业研究机构项目，本次华为申请不需要控制或获取心率、心电图、PPG 等人体传感器原始数据。运动后复盘如需展示心率等健康数据，应优先通过用户明确授权的 Health Kit / Health Service Kit 标准健康数据接口读取汇总数据，并在后续单独提交健康数据权限申请、隐私政策和用户授权路径。</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
         <x:v>不申请，暂无截图</x:v>
@@ -645,8 +645,8 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>使用场景：本项目当前首发范围为 Apple Watch / watchOS 徒步导航 MVP，华为生态仅作为 Apple Watch MVP 之后的平台验证预研。手机侧验证 App 在用户主动打开并选择徒步路线后，需要发现并确认已配对的 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，读取设备随机标识符、名称、电量、连接状态、应用安装状态等基础信息，用于判断是否可以向目标手表下发路线数据；当设备在线但未安装验证端应用时，在手机侧提示用户先安装或打开对应手表端验证应用；当设备在线且验证端应用可用时，才允许用户手动发起路线同步。
-需求：计划先验证 HarmonyOS / 华为手机线，随后验证非华为 Android 手机线；不把 iPhone + 华为手表作为深度联动主路径。需要在 WATCH 5 / WATCH 4 上验证完整手表 App，在 WATCH GT 6 / GT 5 上验证轻量应用或手机协同路径。手机侧与手表侧通信只在用户主动进入路线同步/徒步验证流程时使用，申请材料中的能力均为待华为真机与 AGC 后台验证，不代表已上线或已实测结论。</x:v>
+        <x:v>使用场景：本次申请仅针对华为穿戴生态的户外徒步手表应用验证与后续上线准备。手机侧应用在用户主动打开并选择徒步路线后，需要发现并确认已配对的 HUAWEI WATCH 数字系列或 HUAWEI WATCH GT 系列设备，读取设备随机标识符、名称、电量、连接状态、应用安装状态等基础信息，用于判断是否可以向目标手表下发路线数据；当设备在线但未安装手表端应用或轻量协同能力不可用时，在手机侧提示用户先安装或打开对应手表端应用；当设备在线且手表端能力可用时，才允许用户手动发起路线同步。
+需求：计划先验证 HarmonyOS / 华为手机线，随后验证 Android 手机线。需要在 HUAWEI WATCH 5 / WATCH 4 上验证完整手表 App 路径，在 HUAWEI WATCH GT 6 / GT 5 上验证轻量应用或手机协同路径。手机侧与手表侧通信只在用户主动进入路线同步/徒步验证流程时使用，申请材料中的目标机型和能力仍以华为真机、SDK 文档和 AppGallery Connect 后台审核结果为准。</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
         <x:v>待补充截图：手机侧路线详情页 -&gt; 同步到华为手表 -&gt; 设备选择/连接状态页</x:v>
@@ -663,8 +663,8 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>使用场景：手机侧验证 App 在用户主动选择一条 GPX/路线 payload 并点击“同步到手表”后，向已配对的华为穿戴设备发送路线摘要、路线点位数据或导航指令，并接收手表端 ACK、安装结果、当前会话状态、偏航提醒状态、低电量状态等文本/JSON 消息。该能力用于验证徒步前路线下发、徒步中状态确认、结束后最小结果回传等闭环，不用于营销推送或无用户触发的通知。
-需求：手机侧形态包括 HarmonyOS / 华为手机验证 App 和 Android 手机验证 App；手表侧按 WATCH 数字系列完整应用与 GT 系列轻量/协同路径分别验证。发送内容主要为文本或 JSON；如后续验证 GPX 文件传输，仅限用户选定路线文件，不传输通讯录、相册、账号密码等无关个人数据。发送动作由用户在手机侧主动触发，优先要求手机 App 前台可见，手表端应用或轻量协同能力可用。目标机型优先 WATCH 5 / WATCH 4、WATCH GT 6 / GT 5，实际支持范围以真机和华为后台审核为准。</x:v>
+        <x:v>使用场景：手机侧应用在用户主动选择一条 GPX/路线 payload 并点击“同步到华为手表”后，向已配对的华为穿戴设备发送路线摘要、路线点位数据或导航指令，并接收手表端 ACK、安装结果、当前会话状态、偏航提醒状态、低电量状态等文本/JSON 消息。该能力用于华为手表徒步前路线下发、徒步中状态确认、偏航/低电量提醒状态同步、结束后最小结果回传等闭环，不用于营销推送或无用户触发的通知。
+需求：手机侧形态包括 HarmonyOS / 华为手机应用和 Android 手机应用；手表侧按 HUAWEI WATCH 数字系列完整应用与 WATCH GT 系列轻量/协同路径分别验证。发送内容主要为文本或 JSON；如后续验证 GPX 文件传输，仅限用户选定路线文件，不传输通讯录、相册、账号密码等无关个人数据。发送动作由用户在手机侧主动触发，优先要求手机 App 前台可见，手表端应用或轻量协同能力可用。目标机型优先 WATCH 5 / WATCH 4、WATCH GT 6 / GT 5，实际支持范围以真机和华为后台审核为准。</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
         <x:v>待补充截图：手机侧路线详情页 -&gt; 点击同步 -&gt; 手表端接收路线/ACK 状态页</x:v>
@@ -697,8 +697,8 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>项目说明：本项目是户外徒步手表 App 的产品与技术验证项目。当前正式 MVP 主线为 iPhone + Apple Watch：iPhone 负责 GPX 导入、路线详情、路线同步和运动后复盘，Apple Watch 负责腕上地图、路线跟随、偏航提醒、轨迹记录、暂停/继续/结束和结束后回传。
-华为相关申请仅用于 Apple Watch MVP 之后的平台预研，目标是验证 HUAWEI WATCH 数字系列和 WATCH GT 系列是否能承载类似的路线同步、腕上导航提醒、状态回传和运动后复盘闭环。当前华为工程仍为验证骨架，真实设备能力、后台表现、应用安装路径和上架要求均需通过华为真机与 AppGallery Connect 后台确认。
+        <x:v>项目说明：本项目是面向华为穿戴生态的户外徒步手表应用申请与验证材料。应用目标是让用户在华为手机或 Android 手机上导入/选择 GPX 徒步路线，将路线同步到 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，并在手表侧完成路线查看、当前位置确认、偏航提醒、轨迹/状态记录和运动后复盘数据回传。
+华为申请用途：申请 Wear Engine 相关设备基础信息、连接状态、消息通信等能力，用于验证手机与华为穿戴设备之间的路线下发、ACK、状态回传和提醒同步。WATCH 数字系列优先验证完整手表 App 路径，WATCH GT 系列优先验证轻量应用或手机协同路径。具体支持设备、后台表现、应用安装路径和上架要求，以华为真机、SDK 文档和 AppGallery Connect 后台审核结果为准。
 经营/主体说明：请在提交前替换为真实企业或个人开发者简介、经营范围、官网/产品介绍和相关资质。</x:v>
       </x:c>
     </x:row>
@@ -796,9 +796,9 @@
       <x:c r="A3" t="str">
         <x:v>应用名称：待填写正式应用名称。
 应用类型：户外徒步导航、路线记录、运动复盘。
-主要功能：用户在手机侧导入或选择 GPX 徒步路线，查看路线距离、爬升、预计耗时和关键点；在手表侧查看路线、当前位置、方向、实际轨迹和偏航状态；徒步结束后在手机侧查看计划路线与实际轨迹复盘。
-华为验证用途：验证手机侧通过 Wear Engine 向 WATCH / GT 下发路线 payload，手表端回 ACK 和状态，必要时验证运动后轨迹/状态回传。
-待补充截图：路线列表、路线详情、同步到手表、手表路线接收、徒步会话、偏航提醒、结束复盘、授权弹窗。</x:v>
+主要功能：用户在手机侧导入或选择 GPX 徒步路线，查看路线距离、爬升、预计耗时和关键点；通过 Wear Engine 将路线同步到华为手表；在手表侧查看路线、当前位置、方向、实际轨迹和偏航状态；徒步结束后在手机侧查看计划路线与实际轨迹复盘。
+华为申请用途：验证手机侧向 HUAWEI WATCH / WATCH GT 下发路线 payload，手表端回 ACK 和状态，必要时验证运动后轨迹/状态回传。
+待补充截图：路线列表、路线详情、同步到华为手表、设备选择、手表路线接收、徒步会话、偏航提醒、结束复盘、授权弹窗。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -828,7 +828,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>暂无确定采购计划。后续若进入华为真机验证阶段，计划优先准备 HUAWEI WATCH 5 或 WATCH 4、HUAWEI WATCH GT 6 或 GT 5，以及华为手机/非华为 Android 手机测试组合；数量以验证阶段预算为准。</x:v>
+        <x:v>暂无确定采购计划。后续若进入华为真机验证阶段，计划优先准备 HUAWEI WATCH 5 或 WATCH 4、HUAWEI WATCH GT 6 或 GT 5，以及华为手机/Android 手机测试组合；数量以验证阶段预算为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="55.5" customHeight="1">
@@ -836,7 +836,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>暂无已确定的联合华为品牌上线或营销计划。当前申请仅用于技术验证和后续平台适配评估，不在首发 Apple Watch MVP 中对外宣传华为版本能力。</x:v>
+        <x:v>暂无已确定的联合华为品牌上线或营销计划。当前申请用于华为穿戴生态权限申请、技术验证和后续平台适配评估；如后续涉及联合营销，将按华为品牌规范和审核要求另行提交材料。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="62.25" customHeight="1">
@@ -844,7 +844,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>运动类 / 户外徒步导航 / 运动健康辅助复盘。项目不提供医疗诊断，不申请受限开放的人体传感器原始数据能力。</x:v>
+        <x:v>运动类 / 户外徒步导航 / 运动健康辅助复盘。项目不提供医疗诊断，本次不申请受限开放的人体传感器原始数据能力。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/huawei-permission-application/申请数据权限及使用说明-徒步手表项目填写版.xlsx
+++ b/outputs/huawei-permission-application/申请数据权限及使用说明-徒步手表项目填写版.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业开发者" sheetId="1" r:id="R8904ff6be43547d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人开发者" sheetId="2" r:id="Rf02210167ca94ff7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业文字介绍（必填）" sheetId="3" r:id="Rf02f5b2f890e4e88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业项目负责人联系方式（必填）" sheetId="4" r:id="Rcb109e37446b45c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营业执照（选填）" sheetId="5" r:id="Rb02a753f4a9c4583"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用信息（必填）" sheetId="6" r:id="Rbfc7cf9f9d3846ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充说明（必填）" sheetId="7" r:id="R71c38ea27c484834"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业开发者" sheetId="1" r:id="R295a1587ef4641fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人开发者" sheetId="2" r:id="R67f91e7065ef48fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业文字介绍（必填）" sheetId="3" r:id="Rcb9ffd0c84ee4ca7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业项目负责人联系方式（必填）" sheetId="4" r:id="Re3961bb1a41448df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营业执照（选填）" sheetId="5" r:id="R309a5a32d2c64952"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用信息（必填）" sheetId="6" r:id="R411e6ebf232b40ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充说明（必填）" sheetId="7" r:id="R607e7c002be243a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -505,11 +505,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>使用场景：本次申请仅针对华为穿戴生态的户外徒步手表应用验证与后续上线准备。手机侧应用在用户主动打开并选择徒步路线后，需要发现并确认已配对的 HUAWEI WATCH 数字系列或 HUAWEI WATCH GT 系列设备，读取设备随机标识符、名称、电量、连接状态、应用安装状态等基础信息，用于判断是否可以向目标手表下发路线数据；当设备在线但未安装手表端应用或轻量协同能力不可用时，在手机侧提示用户先安装或打开对应手表端应用；当设备在线且手表端能力可用时，才允许用户手动发起路线同步。
-需求：计划先验证 HarmonyOS / 华为手机线，随后验证 Android 手机线。需要在 HUAWEI WATCH 5 / WATCH 4 上验证完整手表 App 路径，在 HUAWEI WATCH GT 6 / GT 5 上验证轻量应用或手机协同路径。手机侧与手表侧通信只在用户主动进入路线同步/徒步验证流程时使用，申请材料中的目标机型和能力仍以华为真机、SDK 文档和 AppGallery Connect 后台审核结果为准。</x:v>
+        <x:v>1. 手机应用形态：计划提交 HarmonyOS / 华为手机应用，并同步准备 Android 手机应用验证路径；主要服务华为手机与华为穿戴设备协同，后续再按审核要求验证非华为 Android 手机兼容性。本次华为申请不以 iOS 作为主要联动路径。
+2. 穿戴设备侧应用：计划在 HUAWEI WATCH 数字系列上开发完整手表端应用；WATCH GT 系列按目标机型能力验证轻量手表应用或手机协同路径。手表端需要和手机侧通信，用于接收路线、返回 ACK、返回连接/电量/会话状态。
+3. 活跃要求：路线同步由用户在手机侧路线详情页主动点击触发，手机应用优先保持前台活跃；手表侧应用在接收路线、确认开始徒步或回传状态时保持可用。不会在用户无感知场景下静默下发路线。
+4. 支持设备型号：首轮目标为 HUAWEI WATCH 5 / WATCH 4 和 HUAWEI WATCH GT 6 / GT 5。其他型号仅在真机和 AppGallery Connect 后台确认支持后再扩展。
+使用场景：用户在手机侧选择 GPX 徒步路线后，应用读取已配对设备的随机标识符、名称、电量、连接状态和应用安装状态，用于展示可同步设备、判断是否需要安装/打开手表端应用、避免向断连或低电量设备发送路线。</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
-        <x:v>待补充截图：手机侧路线详情页 -&gt; 同步到华为手表 -&gt; 设备选择/连接状态页</x:v>
+        <x:v>待补充截图：路线详情页 -&gt; 同步到华为手表 -&gt; 设备选择页，展示设备名称、电量、连接状态、应用安装状态。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="115.5">
@@ -523,11 +526,15 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>使用场景：手机侧应用在用户主动选择一条 GPX/路线 payload 并点击“同步到华为手表”后，向已配对的华为穿戴设备发送路线摘要、路线点位数据或导航指令，并接收手表端 ACK、安装结果、当前会话状态、偏航提醒状态、低电量状态等文本/JSON 消息。该能力用于华为手表徒步前路线下发、徒步中状态确认、偏航/低电量提醒状态同步、结束后最小结果回传等闭环，不用于营销推送或无用户触发的通知。
-需求：手机侧形态包括 HarmonyOS / 华为手机应用和 Android 手机应用；手表侧按 HUAWEI WATCH 数字系列完整应用与 WATCH GT 系列轻量/协同路径分别验证。发送内容主要为文本或 JSON；如后续验证 GPX 文件传输，仅限用户选定路线文件，不传输通讯录、相册、账号密码等无关个人数据。发送动作由用户在手机侧主动触发，优先要求手机 App 前台可见，手表端应用或轻量协同能力可用。目标机型优先 WATCH 5 / WATCH 4、WATCH GT 6 / GT 5，实际支持范围以真机和华为后台审核为准。</x:v>
+        <x:v>1. 手机应用形态：计划提交 HarmonyOS / 华为手机应用，并准备 Android 手机应用验证路径；本次申请面向华为穿戴生态路线同步和徒步状态回传。
+2. 穿戴设备侧应用：HUAWEI WATCH 数字系列计划开发完整手表端应用；WATCH GT 系列按轻量应用或手机协同路径验证。手表端需要和手机侧通信。
+3. 活跃要求：发送路线、导航提示或状态同步均由用户主动操作或徒步会话中的明确状态变化触发；路线下发时手机应用前台活跃，手表侧应用处于可接收状态。
+4. 通知/消息数据格式：主要为文本和 JSON，包括路线 ID、路线名称、距离、爬升、关键点、路线点位摘要、同步 ACK、会话状态、偏航状态、低电量状态等。如后续验证 GPX 文件传输，仅传输用户选定路线文件。
+5. 支持设备型号：首轮目标为 HUAWEI WATCH 5 / WATCH 4、HUAWEI WATCH GT 6 / GT 5，实际范围以真机、SDK 和后台审核结果为准。
+使用场景：用户点击“同步到华为手表”后，手机向手表发送路线数据；手表接收后返回 ACK；徒步过程中手表可回传当前会话状态、偏航提醒状态、低电量状态；结束后回传最小复盘状态。消息不用于营销推送。</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>待补充截图：手机侧路线详情页 -&gt; 点击同步 -&gt; 手表端接收路线/ACK 状态页</x:v>
+        <x:v>待补充截图：路线详情页点击同步、手表端接收路线、ACK/同步成功状态、徒步状态回传页面。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="99">
@@ -542,10 +549,13 @@
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>暂不申请。
-当前华为申请重点是路线下发、ACK、连接/电量状态、手表端路线显示、偏航提醒和轨迹/状态回传。睡眠状态、佩戴状态等信息不作为本次权限申请的必需能力；若后续需要用于“确认用户佩戴手表后再开始徒步记录”等体验优化，将另行补充真实产品页面、用户授权路径和最小化使用说明。</x:v>
+1. 手机应用形态：本次华为申请的核心是路线同步、设备连接状态、消息通信和徒步会话状态回传，不需要读取睡眠状态。
+2. 穿戴设备侧应用：即使开发手表端应用，首轮也不依赖睡眠状态或佩戴状态完成路线同步闭环。
+3. 支持设备型号：不申请此项，暂无目标型号。
+说明：如后续需要在开始徒步前判断“用户是否佩戴手表”，会单独补充真实使用场景、授权路径和最小化数据范围后再申请。</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>不申请，暂无截图</x:v>
+        <x:v>不申请，暂无截图。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="115.5">
@@ -559,11 +569,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>使用场景：在华为手表徒步导航验证过程中，手机侧或手表侧需要读取已配对穿戴设备的加速度、陀螺仪等运动传感器信息，用于验证户外徒步中的运动状态判断、步频/运动趋势辅助分析、偏航提醒可信度辅助判断，以及运动后复盘中的运动片段标注。该数据只用于当前用户本次徒步会话的实时判断和复盘展示，不用于广告画像、与第三方共享或跨用户分析。
-需求：手机侧应用计划覆盖 HarmonyOS / 华为手机和 Android 手机；手表侧优先 WATCH 5 / WATCH 4，GT 6 / GT 5 仅在目标机型和 SDK 支持时验证。传感器采样频率、后台可用性、电量影响和机型差异均需要华为真机验证。若审核认为该能力与首轮路线同步验证无关，可先不申请此项，待户外能力验证阶段再单独申请。</x:v>
+        <x:v>1. 手机应用形态：计划提交 HarmonyOS / 华为手机应用，并准备 Android 手机应用验证路径；该能力仅用于华为手表徒步会话中的运动状态辅助判断。
+2. 穿戴设备侧应用：计划在 HUAWEI WATCH 数字系列上验证完整手表端应用；WATCH GT 系列仅在目标机型和 SDK 支持时验证轻量应用或协同能力。手表端需要与手机侧通信，用于同步会话状态和复盘摘要。
+3. 支持设备型号：优先验证 HUAWEI WATCH 5 / WATCH 4；WATCH GT 6 / GT 5 作为可行性验证对象，实际支持以真机和 SDK 结果为准。
+使用场景：徒步会话进行中，读取加速度、陀螺仪等运动传感器信息，用于辅助判断用户运动状态、步频/运动趋势、偏航提醒可信度和运动后复盘片段标注。数据只用于当前用户本次徒步会话，不用于广告画像、第三方共享或医疗判断。
+备注：若审核认为首轮路线同步不需要运动传感器，可先删除本项，待户外会话能力验证阶段单独申请。</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>待补充截图：徒步会话页/复盘页中的运动状态辅助展示；若首轮不申请则删除本行</x:v>
+        <x:v>待补充截图：徒步会话页或复盘页中运动状态/步频/片段标注展示；如首轮不申请则删除本行。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="99">
@@ -578,10 +591,13 @@
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>暂不申请。
-本项目不是医疗诊断或专业研究机构项目，本次华为申请不需要控制或获取心率、心电图、PPG 等人体传感器原始数据。运动后复盘如需展示心率等健康数据，应优先通过用户明确授权的 Health Kit / Health Service Kit 标准健康数据接口读取汇总数据，并在后续单独提交健康数据权限申请、隐私政策和用户授权路径。</x:v>
+1. 手机应用形态：本项目不是医疗诊断或专业研究机构项目，本次华为申请不需要人体传感器原始数据。
+2. 穿戴设备侧应用：手表端徒步导航、路线同步、偏航提醒和状态回传不依赖心率、心电图、PPG 等原始人体传感器数据。
+3. 支持设备型号：不申请此项，暂无目标型号。
+说明：运动后复盘如需展示心率等健康数据，后续会通过用户明确授权的 Health Kit / Health Service Kit 标准健康数据接口读取汇总数据，并另行提交健康数据权限申请、隐私政策和授权路径。</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>不申请，暂无截图</x:v>
+        <x:v>不申请，暂无截图。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -645,11 +661,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>使用场景：本次申请仅针对华为穿戴生态的户外徒步手表应用验证与后续上线准备。手机侧应用在用户主动打开并选择徒步路线后，需要发现并确认已配对的 HUAWEI WATCH 数字系列或 HUAWEI WATCH GT 系列设备，读取设备随机标识符、名称、电量、连接状态、应用安装状态等基础信息，用于判断是否可以向目标手表下发路线数据；当设备在线但未安装手表端应用或轻量协同能力不可用时，在手机侧提示用户先安装或打开对应手表端应用；当设备在线且手表端能力可用时，才允许用户手动发起路线同步。
-需求：计划先验证 HarmonyOS / 华为手机线，随后验证 Android 手机线。需要在 HUAWEI WATCH 5 / WATCH 4 上验证完整手表 App 路径，在 HUAWEI WATCH GT 6 / GT 5 上验证轻量应用或手机协同路径。手机侧与手表侧通信只在用户主动进入路线同步/徒步验证流程时使用，申请材料中的目标机型和能力仍以华为真机、SDK 文档和 AppGallery Connect 后台审核结果为准。</x:v>
+        <x:v>1. 手机应用形态：计划提交 HarmonyOS / 华为手机应用，并同步准备 Android 手机应用验证路径；主要服务华为手机与华为穿戴设备协同，后续再按审核要求验证非华为 Android 手机兼容性。本次华为申请不以 iOS 作为主要联动路径。
+2. 穿戴设备侧应用：计划在 HUAWEI WATCH 数字系列上开发完整手表端应用；WATCH GT 系列按目标机型能力验证轻量手表应用或手机协同路径。手表端需要和手机侧通信，用于接收路线、返回 ACK、返回连接/电量/会话状态。
+3. 活跃要求：路线同步由用户在手机侧路线详情页主动点击触发，手机应用优先保持前台活跃；手表侧应用在接收路线、确认开始徒步或回传状态时保持可用。不会在用户无感知场景下静默下发路线。
+4. 支持设备型号：首轮目标为 HUAWEI WATCH 5 / WATCH 4 和 HUAWEI WATCH GT 6 / GT 5。其他型号仅在真机和 AppGallery Connect 后台确认支持后再扩展。
+使用场景：用户在手机侧选择 GPX 徒步路线后，应用读取已配对设备的随机标识符、名称、电量、连接状态和应用安装状态，用于展示可同步设备、判断是否需要安装/打开手表端应用、避免向断连或低电量设备发送路线。</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
-        <x:v>待补充截图：手机侧路线详情页 -&gt; 同步到华为手表 -&gt; 设备选择/连接状态页</x:v>
+        <x:v>待补充截图：路线详情页 -&gt; 同步到华为手表 -&gt; 设备选择页，展示设备名称、电量、连接状态、应用安装状态。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="115.5">
@@ -663,11 +682,15 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>使用场景：手机侧应用在用户主动选择一条 GPX/路线 payload 并点击“同步到华为手表”后，向已配对的华为穿戴设备发送路线摘要、路线点位数据或导航指令，并接收手表端 ACK、安装结果、当前会话状态、偏航提醒状态、低电量状态等文本/JSON 消息。该能力用于华为手表徒步前路线下发、徒步中状态确认、偏航/低电量提醒状态同步、结束后最小结果回传等闭环，不用于营销推送或无用户触发的通知。
-需求：手机侧形态包括 HarmonyOS / 华为手机应用和 Android 手机应用；手表侧按 HUAWEI WATCH 数字系列完整应用与 WATCH GT 系列轻量/协同路径分别验证。发送内容主要为文本或 JSON；如后续验证 GPX 文件传输，仅限用户选定路线文件，不传输通讯录、相册、账号密码等无关个人数据。发送动作由用户在手机侧主动触发，优先要求手机 App 前台可见，手表端应用或轻量协同能力可用。目标机型优先 WATCH 5 / WATCH 4、WATCH GT 6 / GT 5，实际支持范围以真机和华为后台审核为准。</x:v>
+        <x:v>1. 手机应用形态：计划提交 HarmonyOS / 华为手机应用，并准备 Android 手机应用验证路径；本次申请面向华为穿戴生态路线同步和徒步状态回传。
+2. 穿戴设备侧应用：HUAWEI WATCH 数字系列计划开发完整手表端应用；WATCH GT 系列按轻量应用或手机协同路径验证。手表端需要和手机侧通信。
+3. 活跃要求：发送路线、导航提示或状态同步均由用户主动操作或徒步会话中的明确状态变化触发；路线下发时手机应用前台活跃，手表侧应用处于可接收状态。
+4. 通知/消息数据格式：主要为文本和 JSON，包括路线 ID、路线名称、距离、爬升、关键点、路线点位摘要、同步 ACK、会话状态、偏航状态、低电量状态等。如后续验证 GPX 文件传输，仅传输用户选定路线文件。
+5. 支持设备型号：首轮目标为 HUAWEI WATCH 5 / WATCH 4、HUAWEI WATCH GT 6 / GT 5，实际范围以真机、SDK 和后台审核结果为准。
+使用场景：用户点击“同步到华为手表”后，手机向手表发送路线数据；手表接收后返回 ACK；徒步过程中手表可回传当前会话状态、偏航提醒状态、低电量状态；结束后回传最小复盘状态。消息不用于营销推送。</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>待补充截图：手机侧路线详情页 -&gt; 点击同步 -&gt; 手表端接收路线/ACK 状态页</x:v>
+        <x:v>待补充截图：路线详情页点击同步、手表端接收路线、ACK/同步成功状态、徒步状态回传页面。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -697,8 +720,12 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>项目说明：本项目是面向华为穿戴生态的户外徒步手表应用申请与验证材料。应用目标是让用户在华为手机或 Android 手机上导入/选择 GPX 徒步路线，将路线同步到 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，并在手表侧完成路线查看、当前位置确认、偏航提醒、轨迹/状态记录和运动后复盘数据回传。
-华为申请用途：申请 Wear Engine 相关设备基础信息、连接状态、消息通信等能力，用于验证手机与华为穿戴设备之间的路线下发、ACK、状态回传和提醒同步。WATCH 数字系列优先验证完整手表 App 路径，WATCH GT 系列优先验证轻量应用或手机协同路径。具体支持设备、后台表现、应用安装路径和上架要求，以华为真机、SDK 文档和 AppGallery Connect 后台审核结果为准。
+        <x:v>项目说明：本项目是面向华为穿戴生态的户外徒步手表应用申请材料。应用目标是让用户在华为手机或 Android 手机上导入/选择 GPX 徒步路线，将路线同步到 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，并在手表侧完成路线查看、当前位置确认、偏航提醒、轨迹/状态记录和运动后复盘数据回传。
+本次申请的权限用途：
+1. 设备基础信息和连接状态：用于识别用户已配对的华为手表、展示设备名称/电量/连接状态、判断是否可以同步路线。
+2. 消息通知/通信：用于用户主动发起路线下发、手表 ACK、徒步状态/偏航/低电量状态回传。
+3. 运动传感器：仅作为可选验证项，用于徒步运动状态辅助判断；如审核认为首轮无关，可暂不申请。
+4. 睡眠/佩戴状态、心率/ECG/PPG 等人体传感器原始数据：本次不申请。
 经营/主体说明：请在提交前替换为真实企业或个人开发者简介、经营范围、官网/产品介绍和相关资质。</x:v>
       </x:c>
     </x:row>
@@ -795,9 +822,13 @@
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>应用名称：待填写正式应用名称。
-应用类型：户外徒步导航、路线记录、运动复盘。
+应用类型：运动类 / 户外徒步导航 / 路线记录 / 运动复盘。
 主要功能：用户在手机侧导入或选择 GPX 徒步路线，查看路线距离、爬升、预计耗时和关键点；通过 Wear Engine 将路线同步到华为手表；在手表侧查看路线、当前位置、方向、实际轨迹和偏航状态；徒步结束后在手机侧查看计划路线与实际轨迹复盘。
-华为申请用途：验证手机侧向 HUAWEI WATCH / WATCH GT 下发路线 payload，手表端回 ACK 和状态，必要时验证运动后轨迹/状态回传。
+数据权限对应功能：
+1. 设备基础信息：设备选择页展示已配对设备、连接状态、电量和应用安装状态。
+2. 消息通信：路线详情页点击同步后下发路线 JSON/GPX 摘要，手表返回 ACK 和会话状态。
+3. 运动传感器：徒步会话中辅助判断运动状态和复盘片段；可按审核要求后置。
+不申请数据：睡眠状态、佩戴状态、心率、ECG、PPG 等人体传感器原始数据。
 待补充截图：路线列表、路线详情、同步到华为手表、设备选择、手表路线接收、徒步会话、偏航提醒、结束复盘、授权弹窗。</x:v>
       </x:c>
     </x:row>

--- a/outputs/huawei-permission-application/申请数据权限及使用说明-徒步手表项目填写版.xlsx
+++ b/outputs/huawei-permission-application/申请数据权限及使用说明-徒步手表项目填写版.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业开发者" sheetId="1" r:id="R295a1587ef4641fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人开发者" sheetId="2" r:id="R67f91e7065ef48fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业文字介绍（必填）" sheetId="3" r:id="Rcb9ffd0c84ee4ca7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业项目负责人联系方式（必填）" sheetId="4" r:id="Re3961bb1a41448df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营业执照（选填）" sheetId="5" r:id="R309a5a32d2c64952"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用信息（必填）" sheetId="6" r:id="R411e6ebf232b40ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充说明（必填）" sheetId="7" r:id="R607e7c002be243a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业开发者" sheetId="1" r:id="Rf62c09358a624019"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人开发者" sheetId="2" r:id="R78694cfb4a50419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业文字介绍（必填）" sheetId="3" r:id="R8d8b61b8002e4fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业项目负责人联系方式（必填）" sheetId="4" r:id="Rb97c8abcf27845d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营业执照（选填）" sheetId="5" r:id="Rba7ad7c46ae74669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用信息（必填）" sheetId="6" r:id="Rb2c2e1b958aa4a55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充说明（必填）" sheetId="7" r:id="R8baaf6afbeb34895"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -590,14 +590,14 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>暂不申请。
-1. 手机应用形态：本项目不是医疗诊断或专业研究机构项目，本次华为申请不需要人体传感器原始数据。
-2. 穿戴设备侧应用：手表端徒步导航、路线同步、偏航提醒和状态回传不依赖心率、心电图、PPG 等原始人体传感器数据。
-3. 支持设备型号：不申请此项，暂无目标型号。
-说明：运动后复盘如需展示心率等健康数据，后续会通过用户明确授权的 Health Kit / Health Service Kit 标准健康数据接口读取汇总数据，并另行提交健康数据权限申请、隐私政策和授权路径。</x:v>
+        <x:v>1. 手机应用形态：计划提交 HarmonyOS / 华为手机应用，并准备 Android 手机应用验证路径；该能力仅用于华为手表徒步运动过程和运动后复盘中的健康运动指标展示。本次申请不以 iOS 作为主要联动路径。
+2. 穿戴设备侧应用：计划在 HUAWEI WATCH 数字系列上验证完整手表端应用；WATCH GT 系列仅在目标机型、SDK 和审核策略支持时验证轻量应用或协同能力。手表端需要与手机侧通信，用于同步徒步会话状态、心率相关运动指标和复盘摘要。
+3. 支持设备型号：优先验证 HUAWEI WATCH 5 / WATCH 4；WATCH GT 6 / GT 5 作为可行性验证对象，实际支持以真机、SDK 和后台审核结果为准。
+使用场景：用户开始徒步会话并明确授权后，应用读取穿戴设备采集的心率相关数据，用于在徒步过程中展示当前心率/心率区间，在运动后复盘页展示心率曲线、平均心率、最高心率和高强度片段，帮助用户了解本次徒步运动负荷。数据仅用于当前用户本人运动记录和复盘展示，不用于医疗诊断、疾病筛查、用药建议、广告画像或向第三方共享。
+说明：本次仅申请运动健康场景所需的心率相关能力；心电图 ECG、PPG 原始波形等更高敏感或受限数据如需申请，将在取得华为确认和必要资质后另行提交。</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>不申请，暂无截图。</x:v>
+        <x:v>待补充截图：徒步会话页中的当前心率/心率区间展示、复盘页中的心率曲线/平均心率/最高心率，以及心率授权弹窗。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -720,12 +720,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>项目说明：本项目是面向华为穿戴生态的户外徒步手表应用申请材料。应用目标是让用户在华为手机或 Android 手机上导入/选择 GPX 徒步路线，将路线同步到 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，并在手表侧完成路线查看、当前位置确认、偏航提醒、轨迹/状态记录和运动后复盘数据回传。
+        <x:v>项目说明：本项目是面向华为穿戴生态的户外徒步手表应用申请材料。应用目标是让用户在华为手机或 Android 手机上导入/选择 GPX 徒步路线，将路线同步到 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，并在手表侧完成路线查看、当前位置确认、偏航提醒、轨迹/状态记录、心率展示和运动后复盘数据回传。
 本次申请的权限用途：
 1. 设备基础信息和连接状态：用于识别用户已配对的华为手表、展示设备名称/电量/连接状态、判断是否可以同步路线。
 2. 消息通知/通信：用于用户主动发起路线下发、手表 ACK、徒步状态/偏航/低电量状态回传。
-3. 运动传感器：仅作为可选验证项，用于徒步运动状态辅助判断；如审核认为首轮无关，可暂不申请。
-4. 睡眠/佩戴状态、心率/ECG/PPG 等人体传感器原始数据：本次不申请。
+3. 运动传感器：用于徒步运动状态辅助判断；如审核认为首轮无关，可按要求后置。
+4. 心率相关数据：用于徒步中当前心率/心率区间展示，以及运动后复盘中的心率曲线、平均心率、最高心率和运动负荷参考。
+5. 睡眠/佩戴状态、心电图 ECG、PPG 原始波形等非本次徒步复盘必需数据：本次不申请。
 经营/主体说明：请在提交前替换为真实企业或个人开发者简介、经营范围、官网/产品介绍和相关资质。</x:v>
       </x:c>
     </x:row>
@@ -823,13 +824,14 @@
       <x:c r="A3" t="str">
         <x:v>应用名称：待填写正式应用名称。
 应用类型：运动类 / 户外徒步导航 / 路线记录 / 运动复盘。
-主要功能：用户在手机侧导入或选择 GPX 徒步路线，查看路线距离、爬升、预计耗时和关键点；通过 Wear Engine 将路线同步到华为手表；在手表侧查看路线、当前位置、方向、实际轨迹和偏航状态；徒步结束后在手机侧查看计划路线与实际轨迹复盘。
+主要功能：用户在手机侧导入或选择 GPX 徒步路线，查看路线距离、爬升、预计耗时和关键点；通过 Wear Engine 将路线同步到华为手表；在手表侧查看路线、当前位置、方向、实际轨迹、偏航状态和运动心率；徒步结束后在手机侧查看计划路线、实际轨迹和心率曲线等复盘信息。
 数据权限对应功能：
 1. 设备基础信息：设备选择页展示已配对设备、连接状态、电量和应用安装状态。
 2. 消息通信：路线详情页点击同步后下发路线 JSON/GPX 摘要，手表返回 ACK 和会话状态。
 3. 运动传感器：徒步会话中辅助判断运动状态和复盘片段；可按审核要求后置。
-不申请数据：睡眠状态、佩戴状态、心率、ECG、PPG 等人体传感器原始数据。
-待补充截图：路线列表、路线详情、同步到华为手表、设备选择、手表路线接收、徒步会话、偏航提醒、结束复盘、授权弹窗。</x:v>
+4. 心率相关数据：徒步中展示当前心率/心率区间，复盘页展示平均心率、最高心率和心率曲线，仅用于运动负荷参考。
+不申请数据：睡眠状态、佩戴状态、心电图 ECG、PPG 原始波形等非本次徒步复盘必需数据。
+待补充截图：路线列表、路线详情、同步到华为手表、设备选择、手表路线接收、徒步会话心率展示、偏航提醒、结束复盘心率曲线、授权弹窗。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -875,7 +877,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>运动类 / 户外徒步导航 / 运动健康辅助复盘。项目不提供医疗诊断，本次不申请受限开放的人体传感器原始数据能力。</x:v>
+        <x:v>运动类 / 户外徒步导航 / 运动健康辅助复盘。项目不提供医疗诊断；心率数据仅用于用户本人徒步运动记录和复盘展示，不用于疾病诊断、治疗建议或专业医疗研究。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/huawei-permission-application/申请数据权限及使用说明-徒步手表项目填写版.xlsx
+++ b/outputs/huawei-permission-application/申请数据权限及使用说明-徒步手表项目填写版.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业开发者" sheetId="1" r:id="Rf62c09358a624019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人开发者" sheetId="2" r:id="R78694cfb4a50419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业文字介绍（必填）" sheetId="3" r:id="R8d8b61b8002e4fe0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业项目负责人联系方式（必填）" sheetId="4" r:id="Rb97c8abcf27845d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营业执照（选填）" sheetId="5" r:id="Rba7ad7c46ae74669"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用信息（必填）" sheetId="6" r:id="Rb2c2e1b958aa4a55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充说明（必填）" sheetId="7" r:id="R8baaf6afbeb34895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业开发者" sheetId="1" r:id="R284f9bcd7bc543e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人开发者" sheetId="2" r:id="R6aca65a3a793429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业文字介绍（必填）" sheetId="3" r:id="R41469168c7184f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="企业项目负责人联系方式（必填）" sheetId="4" r:id="Rb2b8905c697246fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营业执照（选填）" sheetId="5" r:id="Rc439a6ef6ac941c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用信息（必填）" sheetId="6" r:id="R5abb56383ed24360"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充说明（必填）" sheetId="7" r:id="R6ef4f39c1912412f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -590,14 +590,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>1. 手机应用形态：计划提交 HarmonyOS / 华为手机应用，并准备 Android 手机应用验证路径；该能力仅用于华为手表徒步运动过程和运动后复盘中的健康运动指标展示。本次申请不以 iOS 作为主要联动路径。
-2. 穿戴设备侧应用：计划在 HUAWEI WATCH 数字系列上验证完整手表端应用；WATCH GT 系列仅在目标机型、SDK 和审核策略支持时验证轻量应用或协同能力。手表端需要与手机侧通信，用于同步徒步会话状态、心率相关运动指标和复盘摘要。
+        <x:v>1. 手机应用形态：计划提交 HarmonyOS / 华为手机应用，并准备 Android 手机应用验证路径；该能力仅用于华为手表徒步运动过程中的实时运动负荷提醒，以及运动后复盘中的健康运动指标展示。本次申请不以 iOS 作为主要联动路径。
+2. 穿戴设备侧应用：计划在 HUAWEI WATCH 数字系列上验证完整手表端应用；WATCH GT 系列仅在目标机型、SDK 和审核策略支持时验证轻量应用或协同能力。手表端需要与手机侧通信，用于同步徒步会话状态、心率相关运动指标、运动负荷提醒状态和复盘摘要。
 3. 支持设备型号：优先验证 HUAWEI WATCH 5 / WATCH 4；WATCH GT 6 / GT 5 作为可行性验证对象，实际支持以真机、SDK 和后台审核结果为准。
-使用场景：用户开始徒步会话并明确授权后，应用读取穿戴设备采集的心率相关数据，用于在徒步过程中展示当前心率/心率区间，在运动后复盘页展示心率曲线、平均心率、最高心率和高强度片段，帮助用户了解本次徒步运动负荷。数据仅用于当前用户本人运动记录和复盘展示，不用于医疗诊断、疾病筛查、用药建议、广告画像或向第三方共享。
+使用场景：用户开始徒步会话并明确授权后，应用读取穿戴设备采集的心率相关数据，用于徒步过程中展示当前心率/心率区间，并在心率持续处于用户设定或系统建议的高强度区间、长时间爬升或运动负荷偏高时，通过手表震动/提示提醒用户放慢速度、补水或短暂休息；运动结束后，在复盘页展示心率曲线、平均心率、最高心率、高强度片段和休息提醒记录，帮助用户了解本次徒步运动负荷和节奏安排。
+数据边界：心率数据仅用于当前用户本人徒步过程提醒、运动记录和复盘展示，不用于医疗诊断、疾病筛查、用药建议、广告画像或向第三方共享。休息提醒属于运动负荷和体感安全辅助提醒，不作为医疗判断或急救建议。
 说明：本次仅申请运动健康场景所需的心率相关能力；心电图 ECG、PPG 原始波形等更高敏感或受限数据如需申请，将在取得华为确认和必要资质后另行提交。</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>待补充截图：徒步会话页中的当前心率/心率区间展示、复盘页中的心率曲线/平均心率/最高心率，以及心率授权弹窗。</x:v>
+        <x:v>待补充截图：徒步会话页中的当前心率/心率区间展示、高心率或高强度持续时的休息提醒、复盘页中的心率曲线/平均心率/最高心率/提醒记录，以及心率授权弹窗。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -720,13 +721,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>项目说明：本项目是面向华为穿戴生态的户外徒步手表应用申请材料。应用目标是让用户在华为手机或 Android 手机上导入/选择 GPX 徒步路线，将路线同步到 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，并在手表侧完成路线查看、当前位置确认、偏航提醒、轨迹/状态记录、心率展示和运动后复盘数据回传。
+        <x:v>项目说明：本项目是面向华为穿戴生态的户外徒步手表应用申请材料。应用目标是让用户在华为手机或 Android 手机上导入/选择 GPX 徒步路线，将路线同步到 HUAWEI WATCH 数字系列或 WATCH GT 系列设备，并在手表侧完成路线查看、当前位置确认、偏航提醒、轨迹/状态记录、心率展示、休息提醒和运动后复盘数据回传。
 本次申请的权限用途：
 1. 设备基础信息和连接状态：用于识别用户已配对的华为手表、展示设备名称/电量/连接状态、判断是否可以同步路线。
-2. 消息通知/通信：用于用户主动发起路线下发、手表 ACK、徒步状态/偏航/低电量状态回传。
+2. 消息通知/通信：用于用户主动发起路线下发、手表 ACK、徒步状态/偏航/低电量/休息提醒状态回传。
 3. 运动传感器：用于徒步运动状态辅助判断；如审核认为首轮无关，可按要求后置。
-4. 心率相关数据：用于徒步中当前心率/心率区间展示，以及运动后复盘中的心率曲线、平均心率、最高心率和运动负荷参考。
-5. 睡眠/佩戴状态、心电图 ECG、PPG 原始波形等非本次徒步复盘必需数据：本次不申请。
+4. 心率相关数据：用于徒步中当前心率/心率区间展示；当心率持续处于高强度区间或运动负荷偏高时提醒用户放慢速度、补水或休息；运动后复盘中展示心率曲线、平均心率、最高心率、高强度片段和提醒记录。
+5. 睡眠/佩戴状态、心电图 ECG、PPG 原始波形等非本次徒步场景必需数据：本次不申请。
 经营/主体说明：请在提交前替换为真实企业或个人开发者简介、经营范围、官网/产品介绍和相关资质。</x:v>
       </x:c>
     </x:row>
@@ -824,14 +825,14 @@
       <x:c r="A3" t="str">
         <x:v>应用名称：待填写正式应用名称。
 应用类型：运动类 / 户外徒步导航 / 路线记录 / 运动复盘。
-主要功能：用户在手机侧导入或选择 GPX 徒步路线，查看路线距离、爬升、预计耗时和关键点；通过 Wear Engine 将路线同步到华为手表；在手表侧查看路线、当前位置、方向、实际轨迹、偏航状态和运动心率；徒步结束后在手机侧查看计划路线、实际轨迹和心率曲线等复盘信息。
+主要功能：用户在手机侧导入或选择 GPX 徒步路线，查看路线距离、爬升、预计耗时和关键点；通过 Wear Engine 将路线同步到华为手表；在手表侧查看路线、当前位置、方向、实际轨迹、偏航状态、运动心率和休息提醒；徒步结束后在手机侧查看计划路线、实际轨迹、心率曲线和休息提醒记录等复盘信息。
 数据权限对应功能：
 1. 设备基础信息：设备选择页展示已配对设备、连接状态、电量和应用安装状态。
 2. 消息通信：路线详情页点击同步后下发路线 JSON/GPX 摘要，手表返回 ACK 和会话状态。
 3. 运动传感器：徒步会话中辅助判断运动状态和复盘片段；可按审核要求后置。
-4. 心率相关数据：徒步中展示当前心率/心率区间，复盘页展示平均心率、最高心率和心率曲线，仅用于运动负荷参考。
-不申请数据：睡眠状态、佩戴状态、心电图 ECG、PPG 原始波形等非本次徒步复盘必需数据。
-待补充截图：路线列表、路线详情、同步到华为手表、设备选择、手表路线接收、徒步会话心率展示、偏航提醒、结束复盘心率曲线、授权弹窗。</x:v>
+4. 心率相关数据：徒步中展示当前心率/心率区间；当心率持续处于高强度区间或运动负荷偏高时提醒用户放慢、补水或休息；复盘页展示平均心率、最高心率、心率曲线和提醒记录，仅用于运动负荷参考。
+不申请数据：睡眠状态、佩戴状态、心电图 ECG、PPG 原始波形等非本次徒步场景必需数据。
+待补充截图：路线列表、路线详情、同步到华为手表、设备选择、手表路线接收、徒步会话心率展示、休息提醒、偏航提醒、结束复盘心率曲线/提醒记录、授权弹窗。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -877,7 +878,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>运动类 / 户外徒步导航 / 运动健康辅助复盘。项目不提供医疗诊断；心率数据仅用于用户本人徒步运动记录和复盘展示，不用于疾病诊断、治疗建议或专业医疗研究。</x:v>
+        <x:v>运动类 / 户外徒步导航 / 运动健康辅助复盘。项目不提供医疗诊断；心率数据仅用于用户本人徒步过程中的运动负荷展示、休息提醒和运动后复盘，不用于疾病诊断、治疗建议或专业医疗研究。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
